--- a/Data/EXCEL/Transfer/salemon/20240711/6735-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6735-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBB3FDB4-F982-482F-8FBD-535DDC011A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AE959DA-9FE5-4D07-B369-ED044D3E3583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{1E2759CC-A5CE-4F96-880F-3307543ECC5F}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{29F7C37F-6659-4D5B-BE95-681CABBF3FB5}"/>
   </bookViews>
   <sheets>
     <sheet name="6735-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,23 +1261,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E74AC078-C3F1-4F2C-AF8E-1A34B54B464E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70469AF-FEB9-4743-BFDB-C13AC03898C0}">
   <dimension ref="A1:Q87"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1304,7 +1304,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1386,7 +1386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1425,7 +1425,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>181.8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>229.4</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>258.3</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>239.5</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>185.7</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>266.5</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>-45.2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>-53</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>-60.5</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>-66.599999999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>-69.099999999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>-69</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>-70.5</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>-74.099999999999994</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>-74.599999999999994</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>-71.599999999999994</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>-58.1</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>-66.2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>-4.4400000000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>-0.93</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>8.07</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>-5.14</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>33.299999999999997</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>34.9</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>33.4</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>61.9</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>89.4</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>114.4</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3545,217 +3545,217 @@
         <v>93.6</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="10">
         <v>44256</v>
       </c>
